--- a/output/pdf_financials_xlsx/FA.xlsx
+++ b/output/pdf_financials_xlsx/FA.xlsx
@@ -1758,37 +1758,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.16679</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.657205</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.377721</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.298522</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.414192</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.335537</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.959077</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.469228</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.655703</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.428869</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.155081</v>
       </c>
     </row>
     <row r="35">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.20679</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.697205</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.377721</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.04</v>
+        <v>1.338522</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.04</v>
+        <v>1.454192</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.375537</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.04</v>
+        <v>2.999077</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.04</v>
+        <v>1.509228</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.695703</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.468869</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.04</v>
+        <v>2.195081</v>
       </c>
     </row>
     <row r="37">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/FA.xlsx
+++ b/output/pdf_financials_xlsx/FA.xlsx
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.021757</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.144665</v>
+        <v>2.166422</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-5.415329</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>34.02379912130324</v>
+        <v>34.36896062553919</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>231.5638483017545</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.021757</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -5097,37 +5097,37 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>1.837754</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.815025</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.929701</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>3.673919</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>28.872314</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>14.697673</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>14.225589</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>5.093711</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>4.219134</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>3.643413</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>8.160204999999999</v>
       </c>
     </row>
     <row r="116">
@@ -11954,7 +11954,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -12139,7 +12143,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -16502,7 +16510,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -16847,7 +16859,11 @@
           <t>Proceeds from shares issued $</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -17693,7 +17709,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E172" s="5" t="n">
         <v>2.498722</v>
       </c>
@@ -18318,7 +18338,11 @@
           <t>Proceeds from shares issued $</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -19316,7 +19340,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" s="5" t="n">
         <v>0.021757</v>
       </c>
@@ -20014,7 +20042,11 @@
           <t>Proceeds from sale of public investments</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E205" s="5" t="n">
         <v>1.837754</v>
       </c>
@@ -20298,7 +20330,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E209" s="5" t="n">
         <v>2.15</v>
       </c>
